--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Реестр тестов" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Регламент релиза" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Правила" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Пропуски смока" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1115,4 +1116,686 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="64" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Формы, исключённые из смок-теста (ПропускаемыеФормы обработки СмокТест)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Форма</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Причина</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Добавлено</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Справочник.СерииНоменклатуры.Форма.УстановкаСерий</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный параметр формы (Ссылка)</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Справочник.СерииНоменклатуры.Форма.ВыборСерииПоОстаткам</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный параметр формы (ДатаОстатков)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Справочник.УпаковкиЕдиницыИзмерения.Форма.ФормаВыбораИзДокументов</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный параметр формы (Номенклатура)</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Документ.ЗаказПоставщику.Форма.ПодборПредварительныхЗаказов</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный параметр формы (ЗаказПоставщику)</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Документ.ОперацияБух.Форма.ФормаНастройки</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный параметр формы (адрес временного хранилища)</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Обработка.ГрупповоеИзменениеРеквизитов.Форма.ВыбранныеЭлементы</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный параметр формы (контекст выбранных объектов)</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Обработка.ГрупповоеИзменениеРеквизитов.Форма.РедактированиеФормулы</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный параметр формы (Формула)</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Обработка.ЛичныйКабинетПартнера.Форма.ФормаЗаявкиНаПоискТовара</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный параметр формы (ПоисковыйЗапрос)</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Обработка.ПечатьЭтикеток.Форма.ВыборСерииПоОстаткам</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный параметр формы (ДатаОстатков)</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Обработка.РегистрацияИзмененийДляОбменаДанными.Форма.ВыборКонстанты</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный параметр формы (МассивИменМетаданных)</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Обработка.РегистрацияИзмененийДляОбменаДанными.Форма.ВыборОбъектовОтбором</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный параметр формы (имя таблицы данных)</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Обработка.РегламентныеИФоновыеЗадания.Форма.ДиалогРегламентногоЗадания</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный параметр формы (ИдентификаторЗадания)</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Обработка.РегламентныеИФоновыеЗадания.Форма.ДиалогФоновогоЗадания</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный параметр формы (ИдентификаторЗадания)</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Обработка.РегламентныеИФоновыеЗадания.Форма.ДиалогНастроекСписка</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный параметр формы (Автообновление)</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Обработка.РегламентныеИФоновыеЗадания.Форма.ДиалогОтбораРегламентногоЗадания</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный параметр формы (Отбор)</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Обработка.РегламентныеИФоновыеЗадания.Форма.ДиалогОтбораФоновогоЗадания</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный параметр формы (Отбор)</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>РегистрСведений.РеквизитыКонтрагентов.Форма.ИсторияИзменений</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный параметр формы (Ключ)</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>РегистрСведений.РеквизитыКонтрагентов.Форма.ВводНомераТелефона</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный параметр формы (Значение)</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>РегистрСведений.РеквизитыКонтрагентов.Форма.ВводДополнительныхДанных</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный параметр формы (Комментарий)</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>РегистрНакопления.ТоварыВНаличии.Форма.ВыборПартииПоОстаткам</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный параметр формы (ДатаОстатков)</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>ОбщаяФорма.ВыборЗначений</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный параметр формы (Данные)</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>ОбщаяФорма.ВыборСвязанныхДанных</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный параметр формы (ДанныеСтроки)</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>ОбщаяФорма.ПредварительныйПросмотр</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный параметр формы (Таб)</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>ОбщаяФорма.ПодборОбъектовРасчётовПоОстаткам</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный параметр формы (ДатаСреза)</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>ОбщаяФорма.РедактированиеНДСПлатёжногоДокумента</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный параметр формы (РасшифровкаНДС)</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>ОбщаяФорма.ФормаНастройки1ССканерыШтрихкода</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный параметр формы (ПараметрыОборудования)</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>ОбщаяФорма.ФормаНастройкиУниверсальныйДрайвер</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный параметр формы (ПараметрыОборудования)</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>ОбщаяФорма.ФормаОтчёта</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Платформа: форма отчёта доступна только для конкретного отчёта</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Документ.ВозвратПоставщику.Форма.ФормаДокумента</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Создание нового запрещено: только вводом на основании</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Документ.ВозвратПоставщикуНалоговый.Форма.ФормаДокумента</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Создание нового запрещено: только вводом на основании</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Документ.ВыплатаЗарплаты.Форма.ФормаДокумента</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Создание нового запрещено: только на основании начисления зарплаты</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>ПланВидовХарактеристик.ВидыНастроекПользователей.Форма.ФормаЭлемента</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Нет права интерактивного добавления (пополняется программно)</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>ПланВидовХарактеристик.ВидыНастроекПользователей.Форма.ФормаГруппы</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Нет права интерактивного добавления (пополняется программно)</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>ПланВидовХарактеристик.ВидыРеквизитовКонтрагентов.Форма.ФормаЭлемента</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Нет права интерактивного добавления (пополняется программно)</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>ПланВидовХарактеристик.ВидыСубконтоХозрасчетные.Форма.ФормаЭлемента</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Нет права интерактивного добавления (пополняется программно)</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>ПланСчетов.Хозрасчетный.Форма.ФормаСчета</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Нет права интерактивного добавления (план счетов предопределён)</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Обработка.ГрупповоеИзменениеРеквизитов.Форма.Форма</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Обработка запрещает запуск при включённом режиме совместимости (до поднятия compatibilityMode)</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Источник: ПропускаемыеФормы() в модуле формы обработки СмокТест. Первый полный прогон: 421 форма, 48 ошибок, из них 37 пропусков и 11 дефектов.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -1124,7 +1124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="64" customWidth="1" min="1" max="1"/>
@@ -1786,7 +1786,24 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Справочник.ВариантыВыходаНаРаботу.Форма.ФормаЭлемента</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Нет права интерактивного добавления (Insert=false у Администратора, решение предка)</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>Источник: ПропускаемыеФормы() в модуле формы обработки СмокТест. Первый полный прогон: 421 форма, 48 ошибок, из них 37 пропусков и 11 дефектов.</t>
         </is>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -804,7 +804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -982,24 +982,47 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
+          <t>Проверка обновления на копии базы предыдущей версии: механизм ОбновлениеПрограммы поднимает версию базы, ранее выполненные заполнения данных 1.0.11.x повторно не выполняются, после входа показывается «Что нового»</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Человек</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Версия в регистре ВерсииПодсистем равна версии конфигурации; в журнале регистрации по событию «Обновление программы» нет ошибок</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
           <t>Версия в Configuration.mdo, сборка scripts/dist-build.sh, merge в main, тег, GitHub Release</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Человек (сборку может машина)</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>CF/CFU приложены к релизу</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Полный чек-лист релиза — docs/RELEASING.md; регламент тестов — docs/TESTING.md.</t>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Полный чек-лист релиза — docs/RELEASING.md; регламент тестов — docs/TESTING.md. Секция описания изменений новой версии заполняется в макете ОписаниеИзменений до сборки CF, выгрузка для хаба — scripts/changelog.sh.</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1129,7 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Обновлено: 2026-08-25. Данные согласованы с docs/TESTING.md.</t>
+          <t>Обновлено: 2026-08-26. Данные согласованы с docs/TESTING.md.</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -598,37 +598,37 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Проверка конфигурации</t>
+          <t>Сверка ссылок</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>CheckConfig</t>
+          <t>refcheck</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Ссылочная целостность метаданных, компилируемость модулей (тонкий клиент, сервер)</t>
+          <t>Обращения к объектам, которых нет в конфигурации: константы, перечисления, регистры, картинки, формы и макеты в строковых именах, экспортные методы общих модулей. Компилируется, но падает в рантайме.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>scripts/smoke.sh, шаг 1 (DESIGNER /CheckConfig)</t>
+          <t>scripts/refcheck.py</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>build/check-config.log — непустой лог = провал</t>
+          <t>Вывод в терминал; известные расхождения — scripts/refcheck-known.txt</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Машина — на build/ib; человек — на базах клиентов</t>
+          <t>Машина (Claude) — после каждой правки модулей</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -645,32 +645,32 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Смок-тест форм</t>
+          <t>Проверка конфигурации</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>СмокТест: «открыть все формы»</t>
+          <t>CheckConfig</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>ПриСозданииНаСервере каждой формы конфигурации: картинки БиблиотекиКартинок, запросы динсписков, программное построение, обращения к реквизитам. Мобильные формы пропускаются</t>
+          <t>Ссылочная целостность метаданных, компилируемость модулей (тонкий клиент, сервер)</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>scripts/smoke.sh, шаг 2 (ENTERPRISE /C "СмокТест;отчёт"); интерактивно — открыть обработку СмокТест</t>
+          <t>scripts/smoke.sh, шаг 1 (DESIGNER /CheckConfig)</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>build/smoke-report.txt: строки ОШИБКА;форма;описание + ИТОГ;Всего=N;Ошибок=M; клиентский лог build/smoke-client.log</t>
+          <t>build/check-config.log — непустой лог = провал</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -692,101 +692,149 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Жизненный цикл документов</t>
+          <t>Смок-тест форм</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Создание / запись / проведение</t>
+          <t>СмокТест: формы и печатные формы</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Ключевые документы (ЗаказПокупателя, РеализацияТоваровУслуг, выпуск продукции): создание, заполнение, запись, проведение, движения по регистрам — в транзакции с откатом</t>
+          <t>Проход 1: ПриСозданииНаСервере каждой формы конфигурации (картинки, динсписки, программное построение). Проход 2: формирование всех печатных форм объектов из ПечатныеФормы.ОбъектыСКомандамиПечати() по образцу из базы.</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>План: серверные тесты (обработка или YAxUnit)</t>
+          <t>scripts/smoke.sh, шаг 2 (ENTERPRISE /C "СмокТест;отчёт"); интерактивно — открыть обработку СмокТест</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>build/smoke-report.txt: СТАРТ; ОШИБКА;что;описание; ПУСТО;печатная форма; ПРОПУСК;что;причина; ИТОГ;Всего=N;Ошибок=M;ПечатныхФорм=K;ОшибокПечати=L</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Машина; на живой базе — вне рабочего времени (блокировки)</t>
+          <t>Машина — на build/ib; человек — на базах клиентов</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Нет (откат транзакции)</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>План: при появлении потребности</t>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Реализован</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Жизненный цикл документов</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Создание / запись / проведение</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Ключевые документы (ЗаказПокупателя, РеализацияТоваровУслуг, выпуск продукции): создание, заполнение, запись, проведение, движения по регистрам — в транзакции с откатом</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>План: серверные тесты (обработка или YAxUnit)</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Машина; на живой базе — вне рабочего времени (блокировки)</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Нет (откат транзакции)</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>План: при появлении потребности</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Сценарные UI-тесты</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Тест-клиент платформы / Vanessa Automation</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Клиентская логика: обработчики ПриИзменении, подборы, команды форм, сквозные сценарии</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>План: 1cv8 /TESTCLIENT + управляющий сценарий</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>Машина готовит сценарии, человек контролирует прогон</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>Да — только на копии базы</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>План: при появлении ломающихся клиентских сценариев</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Обновлено: 2026-08-25. Источник: docs/TESTING.md (регламент), scripts/smoke.sh, scripts/lint.sh. Реестр ведёт машина по итогам каждого изменения состава тестов.</t>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Обновлено: 2026-08-26. Источник: docs/TESTING.md (регламент)</t>
         </is>
       </c>
     </row>
@@ -850,7 +898,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>scripts/lint.sh — статический анализ всех модулей</t>
+          <t>scripts/lint.sh — статический анализ всех модулей; scripts/refcheck.py — сверка ссылок с деревом метаданных</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -860,7 +908,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Нет новых замечаний против build/bsl-json-baseline.json</t>
+          <t>Нет новых замечаний против build/bsl-json-baseline.json; сверка ссылок без новых расхождений</t>
         </is>
       </c>
     </row>
@@ -916,7 +964,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>scripts/smoke.sh на обновлённой build/ib: CheckConfig + смок «открыть все формы»</t>
+          <t>scripts/smoke.sh на обновлённой build/ib: CheckConfig + смок форм + смок печатных форм</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -1018,7 +1066,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
@@ -1040,7 +1087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1126,8 +1173,33 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Известные расхождения сверки ссылок</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>scripts/refcheck-known.txt хранит принятые расхождения (стандартные картинки платформы, наследие бухгалтерского контура). Новое расхождение = ошибка: разбирается до сдачи, в файл попадает только с записью причины в docs/TECHDEBT.md.</t>
+        </is>
+      </c>
+    </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Пропуски смока печатных форм</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Печатная форма, которую нельзя проверить без параметров команды, вносится в ПропускаемыеПечатныеФормы() обработки СмокТест с причиной; пустой результат печати пишется строкой ПУСТО и ошибкой не считается.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>Обновлено: 2026-08-26. Данные согласованы с docs/TESTING.md.</t>
         </is>
@@ -1147,7 +1219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="64" customWidth="1" min="1" max="1"/>
@@ -1556,12 +1628,12 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>ОбщаяФорма.ПредварительныйПросмотр</t>
+          <t>ОбщаяФорма.ПодборОбъектовРасчётовПоОстаткам</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Обязательный параметр формы (Таб)</t>
+          <t>Обязательный параметр формы (ДатаСреза)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -1573,12 +1645,12 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>ОбщаяФорма.ПодборОбъектовРасчётовПоОстаткам</t>
+          <t>ОбщаяФорма.РедактированиеНДСПлатёжногоДокумента</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Обязательный параметр формы (ДатаСреза)</t>
+          <t>Обязательный параметр формы (РасшифровкаНДС)</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -1590,12 +1662,12 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>ОбщаяФорма.РедактированиеНДСПлатёжногоДокумента</t>
+          <t>ОбщаяФорма.ФормаНастройки1ССканерыШтрихкода</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Обязательный параметр формы (РасшифровкаНДС)</t>
+          <t>Обязательный параметр формы (ПараметрыОборудования)</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -1607,7 +1679,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>ОбщаяФорма.ФормаНастройки1ССканерыШтрихкода</t>
+          <t>ОбщаяФорма.ФормаНастройкиУниверсальныйДрайвер</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1624,12 +1696,12 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>ОбщаяФорма.ФормаНастройкиУниверсальныйДрайвер</t>
+          <t>ОбщаяФорма.ФормаОтчёта</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Обязательный параметр формы (ПараметрыОборудования)</t>
+          <t>Платформа: форма отчёта доступна только для конкретного отчёта</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -1641,12 +1713,12 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>ОбщаяФорма.ФормаОтчёта</t>
+          <t>Документ.ВозвратПоставщику.Форма.ФормаДокумента</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Платформа: форма отчёта доступна только для конкретного отчёта</t>
+          <t>Создание нового запрещено: только вводом на основании</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -1658,7 +1730,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Документ.ВозвратПоставщику.Форма.ФормаДокумента</t>
+          <t>Документ.ВозвратПоставщикуНалоговый.Форма.ФормаДокумента</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1675,12 +1747,12 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Документ.ВозвратПоставщикуНалоговый.Форма.ФормаДокумента</t>
+          <t>Документ.ВыплатаЗарплаты.Форма.ФормаДокумента</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Создание нового запрещено: только вводом на основании</t>
+          <t>Создание нового запрещено: только на основании начисления зарплаты</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -1692,12 +1764,12 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Документ.ВыплатаЗарплаты.Форма.ФормаДокумента</t>
+          <t>ПланВидовХарактеристик.ВидыНастроекПользователей.Форма.ФормаЭлемента</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Создание нового запрещено: только на основании начисления зарплаты</t>
+          <t>Нет права интерактивного добавления (пополняется программно)</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -1709,7 +1781,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>ПланВидовХарактеристик.ВидыНастроекПользователей.Форма.ФормаЭлемента</t>
+          <t>ПланВидовХарактеристик.ВидыНастроекПользователей.Форма.ФормаГруппы</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1726,7 +1798,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>ПланВидовХарактеристик.ВидыНастроекПользователей.Форма.ФормаГруппы</t>
+          <t>ПланВидовХарактеристик.ВидыРеквизитовКонтрагентов.Форма.ФормаЭлемента</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1743,7 +1815,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>ПланВидовХарактеристик.ВидыРеквизитовКонтрагентов.Форма.ФормаЭлемента</t>
+          <t>ПланВидовХарактеристик.ВидыСубконтоХозрасчетные.Форма.ФормаЭлемента</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1760,12 +1832,12 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>ПланВидовХарактеристик.ВидыСубконтоХозрасчетные.Форма.ФормаЭлемента</t>
+          <t>ПланСчетов.Хозрасчетный.Форма.ФормаСчета</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Нет права интерактивного добавления (пополняется программно)</t>
+          <t>Нет права интерактивного добавления (план счетов предопределён)</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -1777,12 +1849,12 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>ПланСчетов.Хозрасчетный.Форма.ФормаСчета</t>
+          <t>Обработка.ГрупповоеИзменениеРеквизитов.Форма.Форма</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Нет права интерактивного добавления (план счетов предопределён)</t>
+          <t>Обработка запрещает запуск при включённом режиме совместимости (до поднятия compatibilityMode)</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -1791,42 +1863,26 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>Обработка.ГрупповоеИзменениеРеквизитов.Форма.Форма</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>Обработка запрещает запуск при включённом режиме совместимости (до поднятия compatibilityMode)</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
+    <row r="39"/>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Справочник.ВариантыВыходаНаРаботу.Форма.ФормаЭлемента</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Нет права интерактивного добавления (Insert=false у Администратора, решение предка)</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>Справочник.ВариантыВыходаНаРаботу.Форма.ФормаЭлемента</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>Нет права интерактивного добавления (Insert=false у Администратора, решение предка)</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="inlineStr">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>Источник: ПропускаемыеФормы() в модуле формы обработки СмокТест. Первый полный прогон: 421 форма, 48 ошибок, из них 37 пропусков и 11 дефектов.</t>
         </is>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -830,7 +830,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
@@ -1087,7 +1086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1197,9 +1196,21 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Где живут тесты</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Объекты тестов — в подсистеме «Автотесты» (обработка СмокТест и общий модуль АвтотестыКлиент); подсистема не входит в командный интерфейс. Серверная логика прогона — в модуле менеджера обработки, модуль формы только запускает прогон и пишет отчёт. Скрипты — в scripts/.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>Обновлено: 2026-08-26. Данные согласованы с docs/TESTING.md.</t>
         </is>
@@ -1863,7 +1874,6 @@
         </is>
       </c>
     </row>
-    <row r="39"/>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Регламент релиза" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Правила" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Пропуски смока" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Покрытие печати" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1208,7 +1209,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
@@ -1904,4 +1904,553 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>План: объекты печати без образца в тестовой базе (прогон пишет по ним ПРОПУСК)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Объект</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Печатные формы</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Что нужно</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Документ.ВозвратОтПокупателя</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>накладная возврата</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Завести в build/ib один заполненный документ (проведённый, где требуется)</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Нет образца</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Документ.ВозвратОтПокупателяНалоговый</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>накладная возврата</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Завести в build/ib один заполненный документ (проведённый, где требуется)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Нет образца</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Документ.ВыплатаЗарплаты</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>ведомость</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Завести в build/ib один заполненный документ (проведённый, где требуется)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Нет образца</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Документ.ЗаказПоставщику</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>заказ поставщику</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Завести в build/ib один заполненный документ (проведённый, где требуется)</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Нет образца</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Документ.КассоваяСмена</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Z-отчёт</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Завести в build/ib один заполненный документ (проведённый, где требуется)</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Нет образца</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Документ.КорректировкаДолга</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>акт корректировки</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Завести в build/ib один заполненный документ (проведённый, где требуется)</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Нет образца</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Документ.НалоговаяНакладная</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>налоговая накладная</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Завести в build/ib один заполненный документ (проведённый, где требуется)</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Нет образца</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Документ.НалоговаяНакладнаяПокупка</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>налоговая накладная покупки</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Завести в build/ib один заполненный документ (проведённый, где требуется)</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Нет образца</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Документ.ОприходованиеТоваров</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>акт оприходования</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Завести в build/ib один заполненный документ (проведённый, где требуется)</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Нет образца</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Документ.ОтгрузкаТовара</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>накладная на отгрузку</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Завести в build/ib один заполненный документ (проведённый, где требуется)</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Нет образца</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Документ.ПередачаВПереработку</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>накладная на передачу</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Завести в build/ib один заполненный документ (проведённый, где требуется)</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Нет образца</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Документ.ПеремещениеТоваров</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>накладная на перемещение</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Завести в build/ib один заполненный документ (проведённый, где требуется)</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Нет образца</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Документ.ПлатёжнаяВедомостьНаАванс</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>ведомость на аванс</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Завести в build/ib один заполненный документ (проведённый, где требуется)</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Нет образца</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Документ.ПоступлениеИзПереработки</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>накладная на поступление</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Завести в build/ib один заполненный документ (проведённый, где требуется)</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Нет образца</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Документ.ПредложениеПоставщика</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>предложение</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Завести в build/ib один заполненный документ (проведённый, где требуется)</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Нет образца</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Документ.ПриходныйКассовыйОрдер</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>ордер, квитанция</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Завести в build/ib один заполненный документ (проведённый, где требуется)</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Нет образца</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Документ.РасходныйКассовыйОрдер</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>ордер</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Завести в build/ib один заполненный документ (проведённый, где требуется)</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Нет образца</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Документ.СверкаВзаиморасчётов</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>акт сверки</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Завести в build/ib один заполненный документ (проведённый, где требуется)</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Нет образца</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Документ.СписаниеТоваров</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>акт списания</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Завести в build/ib один заполненный документ (проведённый, где требуется)</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Нет образца</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Документ.ТабельУчётаРабочегоВремени</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>табель</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Завести в build/ib один заполненный документ (проведённый, где требуется)</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Нет образца</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Документ.УстановкаЦенНоменклатуры</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>прайс-лист</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Завести в build/ib один заполненный документ (проведённый, где требуется)</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Нет образца</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>РегистрСведений.Лиды</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>заказ и накладная по лиду</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Завести в build/ib один заполненный документ (проведённый, где требуется)</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Нет образца</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n"/>
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Обновлено: 2026-08-26. Источник: docs/TESTING.md, раздел «План: покрытие печати образцами данных».</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n"/>
+      <c r="C26" s="3" t="n"/>
+      <c r="D26" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -708,7 +708,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Проход 1: ПриСозданииНаСервере каждой формы конфигурации (картинки, динсписки, программное построение). Проход 2: формирование всех печатных форм объектов из ПечатныеФормы.ОбъектыСКомандамиПечати() по образцу из базы.</t>
+          <t>Проход 1: ПриСозданииНаСервере каждой формы конфигурации (картинки, динсписки, программное построение). Проход 2: формирование всех печатных форм объектов из ПечатныеФормы.ОбъектыСКомандамиПечати() по образцу из базы; в тексте формы ищется номер документа-образца — если его нет, пишется ПОДОЗРЕНИЕ (пустая шапка).</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>build/smoke-report.txt: СТАРТ; ОШИБКА;что;описание; ПУСТО;печатная форма; ПРОПУСК;что;причина; ИТОГ;Всего=N;Ошибок=M;ПечатныхФорм=K;ОшибокПечати=L</t>
+          <t>build/smoke-report.txt: СТАРТ; ОШИБКА;что;описание; ПУСТО;печатная форма; ПРОПУСК;что;причина; ПОДОЗРЕНИЕ;печатная форма;номера нет; ИТОГ;Всего=N;Ошибок=M;ПечатныхФорм=K;ОшибокПечати=L</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1087,7 +1087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1209,8 +1209,21 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Проверка шапки печатных форм</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Прогон печати ищет в сформированной форме номер документа-образца и пишет строку ПОДОЗРЕНИЕ, если не нашёл: это ловит шапку, собранную из итоговой строки запроса без агрегатных функций. Не ошибка прогона — строки смотрятся глазами. Печатная форма, где номера заведомо нет, вносится в ПечатныеФормыБезНомера() обработки СмокТест с причиной в docs/TESTING.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Обновлено: 2026-08-26. Данные согласованы с docs/TESTING.md.</t>
         </is>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -1087,7 +1087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1221,9 +1221,21 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Образцы для печати</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Печатная форма проверяется только там, где в базе есть объект. Недостающие образцы заводит scripts/fixtures.sh (обработка ТестовыеДанные подсистемы «Автотесты»); скрипт записывает данные — только тестовая база. Новый документ с печатью — правило заполнения образца в ДовестиТоварныйОбразец/ДовестиДенежныйОбразец/ДовестиПрочийОбразец, иначе прогон его печать не увидит.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Обновлено: 2026-08-26. Данные согласованы с docs/TESTING.md.</t>
         </is>
@@ -1937,7 +1949,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>План: объекты печати без образца в тестовой базе (прогон пишет по ним ПРОПУСК)</t>
+          <t>Объекты печати без образца в тестовой базе: образцы заводит scripts/fixtures.sh (обработка ТестовыеДанные). После заполнения прогон печати проверяет их наравне с остальными.</t>
         </is>
       </c>
     </row>
@@ -1976,12 +1988,12 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Завести в build/ib один заполненный документ (проведённый, где требуется)</t>
+          <t>scripts/fixtures.sh заводит образец автоматически</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Нет образца</t>
+          <t>Образец заводится прогоном</t>
         </is>
       </c>
     </row>
@@ -1998,12 +2010,12 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Завести в build/ib один заполненный документ (проведённый, где требуется)</t>
+          <t>scripts/fixtures.sh заводит образец автоматически</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Нет образца</t>
+          <t>Образец заводится прогоном</t>
         </is>
       </c>
     </row>
@@ -2020,12 +2032,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Завести в build/ib один заполненный документ (проведённый, где требуется)</t>
+          <t>scripts/fixtures.sh заводит образец автоматически</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Нет образца</t>
+          <t>Образец заводится прогоном</t>
         </is>
       </c>
     </row>
@@ -2042,12 +2054,12 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Завести в build/ib один заполненный документ (проведённый, где требуется)</t>
+          <t>scripts/fixtures.sh заводит образец автоматически</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Нет образца</t>
+          <t>Образец заводится прогоном</t>
         </is>
       </c>
     </row>
@@ -2064,12 +2076,12 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Завести в build/ib один заполненный документ (проведённый, где требуется)</t>
+          <t>scripts/fixtures.sh заводит образец автоматически</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Нет образца</t>
+          <t>Образец заводится прогоном</t>
         </is>
       </c>
     </row>
@@ -2086,12 +2098,12 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Завести в build/ib один заполненный документ (проведённый, где требуется)</t>
+          <t>scripts/fixtures.sh заводит образец автоматически</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Нет образца</t>
+          <t>Образец заводится прогоном</t>
         </is>
       </c>
     </row>
@@ -2108,12 +2120,12 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Завести в build/ib один заполненный документ (проведённый, где требуется)</t>
+          <t>scripts/fixtures.sh заводит образец автоматически</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Нет образца</t>
+          <t>Образец заводится прогоном</t>
         </is>
       </c>
     </row>
@@ -2130,12 +2142,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Завести в build/ib один заполненный документ (проведённый, где требуется)</t>
+          <t>scripts/fixtures.sh заводит образец автоматически</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Нет образца</t>
+          <t>Образец заводится прогоном</t>
         </is>
       </c>
     </row>
@@ -2152,12 +2164,12 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Завести в build/ib один заполненный документ (проведённый, где требуется)</t>
+          <t>scripts/fixtures.sh заводит образец автоматически</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Нет образца</t>
+          <t>Образец заводится прогоном</t>
         </is>
       </c>
     </row>
@@ -2174,12 +2186,12 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Завести в build/ib один заполненный документ (проведённый, где требуется)</t>
+          <t>scripts/fixtures.sh заводит образец автоматически</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Нет образца</t>
+          <t>Образец заводится прогоном</t>
         </is>
       </c>
     </row>
@@ -2196,12 +2208,12 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Завести в build/ib один заполненный документ (проведённый, где требуется)</t>
+          <t>scripts/fixtures.sh заводит образец автоматически</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Нет образца</t>
+          <t>Образец заводится прогоном</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2230,12 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Завести в build/ib один заполненный документ (проведённый, где требуется)</t>
+          <t>scripts/fixtures.sh заводит образец автоматически</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Нет образца</t>
+          <t>Образец заводится прогоном</t>
         </is>
       </c>
     </row>
@@ -2240,12 +2252,12 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Завести в build/ib один заполненный документ (проведённый, где требуется)</t>
+          <t>scripts/fixtures.sh заводит образец автоматически</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Нет образца</t>
+          <t>Образец заводится прогоном</t>
         </is>
       </c>
     </row>
@@ -2262,12 +2274,12 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Завести в build/ib один заполненный документ (проведённый, где требуется)</t>
+          <t>scripts/fixtures.sh заводит образец автоматически</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Нет образца</t>
+          <t>Образец заводится прогоном</t>
         </is>
       </c>
     </row>
@@ -2284,12 +2296,12 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Завести в build/ib один заполненный документ (проведённый, где требуется)</t>
+          <t>scripts/fixtures.sh заводит образец автоматически</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Нет образца</t>
+          <t>Образец заводится прогоном</t>
         </is>
       </c>
     </row>
@@ -2306,12 +2318,12 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Завести в build/ib один заполненный документ (проведённый, где требуется)</t>
+          <t>scripts/fixtures.sh заводит образец автоматически</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Нет образца</t>
+          <t>Образец заводится прогоном</t>
         </is>
       </c>
     </row>
@@ -2328,12 +2340,12 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Завести в build/ib один заполненный документ (проведённый, где требуется)</t>
+          <t>scripts/fixtures.sh заводит образец автоматически</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Нет образца</t>
+          <t>Образец заводится прогоном</t>
         </is>
       </c>
     </row>
@@ -2350,12 +2362,12 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Завести в build/ib один заполненный документ (проведённый, где требуется)</t>
+          <t>scripts/fixtures.sh заводит образец автоматически</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Нет образца</t>
+          <t>Образец заводится прогоном</t>
         </is>
       </c>
     </row>
@@ -2372,12 +2384,12 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Завести в build/ib один заполненный документ (проведённый, где требуется)</t>
+          <t>scripts/fixtures.sh заводит образец автоматически</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Нет образца</t>
+          <t>Образец заводится прогоном</t>
         </is>
       </c>
     </row>
@@ -2394,12 +2406,12 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Завести в build/ib один заполненный документ (проведённый, где требуется)</t>
+          <t>scripts/fixtures.sh заводит образец автоматически</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Нет образца</t>
+          <t>Образец заводится прогоном</t>
         </is>
       </c>
     </row>
@@ -2416,12 +2428,12 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Завести в build/ib один заполненный документ (проведённый, где требуется)</t>
+          <t>scripts/fixtures.sh заводит образец автоматически</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Нет образца</t>
+          <t>Образец заводится прогоном</t>
         </is>
       </c>
     </row>
@@ -2438,12 +2450,12 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Завести в build/ib один заполненный документ (проведённый, где требуется)</t>
+          <t>scripts/fixtures.sh заводит образец автоматически</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Нет образца</t>
+          <t>Образец заводится прогоном</t>
         </is>
       </c>
     </row>
@@ -2460,8 +2472,16 @@
         </is>
       </c>
       <c r="B26" s="3" t="n"/>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="3" t="n"/>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>scripts/fixtures.sh заводит образец автоматически</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Образец заводится прогоном</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -703,12 +703,12 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>СмокТест: формы и печатные формы</t>
+          <t>СмокТест: формы, формы на образцах и печатные формы</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Проход 1: ПриСозданииНаСервере каждой формы конфигурации (картинки, динсписки, программное построение). Проход 2: формирование всех печатных форм объектов из ПечатныеФормы.ОбъектыСКомандамиПечати() по образцу из базы; в тексте формы ищется номер документа-образца — если его нет, пишется ПОДОЗРЕНИЕ (пустая шапка).</t>
+          <t>Проход 1: ПриСозданииНаСервере каждой формы конфигурации на новом объекте (картинки, динсписки, программное построение). Проход 2: основные формы объекта и группы, открытые с параметром Ключ по образцу из базы, — ветки, работающие только с записанным объектом. Проход 3: формирование всех печатных форм объектов из ПечатныеФормы.ОбъектыСКомандамиПечати() по образцу из базы; в тексте формы ищется номер документа-образца — если его нет, пишется ПОДОЗРЕНИЕ (пустая шапка).</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>build/smoke-report.txt: СТАРТ; ОШИБКА;что;описание; ПУСТО;печатная форма; ПРОПУСК;что;причина; ПОДОЗРЕНИЕ;печатная форма;номера нет; ИТОГ;Всего=N;Ошибок=M;ПечатныхФорм=K;ОшибокПечати=L</t>
+          <t>build/smoke-report.txt: СТАРТ; ОШИБКА;что;описание; ПУСТО;печатная форма; ПРОПУСК;что;причина; ПОДОЗРЕНИЕ;печатная форма;номера нет; ИТОГ;Всего=N;Ошибок=M;НаОбразцах=K;ОшибокНаОбразцах=L;ПечатныхФорм=P;ОшибокПечати=Q. Проверки проходов 2 и 3 помечены префиксами «Образец.» и «Печать.»</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -831,10 +831,11 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Обновлено: 2026-08-26. Источник: docs/TESTING.md (регламент)</t>
+          <t>Обновлено: 2026-08-27. Источник: docs/TESTING.md (регламент)</t>
         </is>
       </c>
     </row>
@@ -1066,6 +1067,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
@@ -1087,7 +1089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1233,11 +1235,23 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>Обновлено: 2026-08-26. Данные согласованы с docs/TESTING.md.</t>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Формы объектов на образцах</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Форма объекта, открытая без параметров, выполняется на новом объекте: ветки «только для записанного объекта» так не проверяются. Проход 2 смока открывает основную форму объекта и группы с параметром Ключ по образцу из базы. Неосновные формы объекта (подставляемые ОбработкойПолученияФормы) проходом не покрыты — во время выполнения форму объекта от формы списка отличить нельзя.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Обновлено: 2026-08-27. Данные согласованы с docs/TESTING.md.</t>
         </is>
       </c>
     </row>
@@ -1899,6 +1913,7 @@
         </is>
       </c>
     </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
@@ -2468,7 +2483,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Обновлено: 2026-08-26. Источник: docs/TESTING.md, раздел «План: покрытие печати образцами данных».</t>
+          <t>Обновлено: 2026-08-27. Источник: docs/TESTING.md, раздел «План: покрытие печати образцами данных».</t>
         </is>
       </c>
       <c r="B26" s="3" t="n"/>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -740,102 +740,149 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Жизненный цикл документов</t>
+          <t>Headless-первый запуск</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Создание / запись / проведение</t>
+          <t>initial-fill: пустая база → заполнение → повтор → смок</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Ключевые документы (ЗаказПокупателя, РеализацияТоваровУслуг, выпуск продукции): создание, заполнение, запись, проведение, движения по регистрам — в транзакции с откатом</t>
+          <t>Обработка НачальноеЗаполнение заводит организацию, пользователей, физлица и служебного администратора из JSON (docs/DEPLOY.md). Тест: пустая база из CF; первое заполнение — success, все created=true, organizations_total и users_total &gt; 0 (визард первого запуска не откроется), слова password в result нет; повтор под созданным администратором — success, всё created=false; scripts/smoke.sh на этой базе — ТЕСТЫ ПРОЙДЕНЫ.</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>План: серверные тесты (обработка или YAxUnit)</t>
+          <t>scripts/initial-fill-test.sh &lt;файл.cf&gt; [каталог-базы] (по умолчанию build/ib-initial); INITIAL_FILL_NO_SMOKE=1 — без смока</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>build/initial-fill-test-1.json, build/initial-fill-test-2.json (result), build/initial-fill-report.txt: СТАРТ; ПРЕДУПРЕЖДЕНИЕ;текст; ИТОГ;Успех=1|0;сводка; клиентский лог build/initial-fill-client.log</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Машина; на живой базе — вне рабочего времени (блокировки)</t>
+          <t>Машина — на build/ib-initial из CF, собранного из обновлённой build/ib; человек — визард глазами на пустой базе (пароль tinycio-1c показывается один раз)</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Нет (откат транзакции)</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>План: при появлении потребности</t>
+          <t>Да — пересоздаёт build/ib-initial; build/ib не трогает. Пароли теста случайные, во временном payload с правами 600, удаляется</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>Реализован</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Жизненный цикл документов</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Создание / запись / проведение</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Ключевые документы (ЗаказПокупателя, РеализацияТоваровУслуг, выпуск продукции): создание, заполнение, запись, проведение, движения по регистрам — в транзакции с откатом</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>План: серверные тесты (обработка или YAxUnit)</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Машина; на живой базе — вне рабочего времени (блокировки)</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Нет (откат транзакции)</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>План: при появлении потребности</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Сценарные UI-тесты</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Тест-клиент платформы / Vanessa Automation</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Клиентская логика: обработчики ПриИзменении, подборы, команды форм, сквозные сценарии</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>План: 1cv8 /TESTCLIENT + управляющий сценарий</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>Машина готовит сценарии, человек контролирует прогон</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>Да — только на копии базы</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>План: при появлении ломающихся клиентских сценариев</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>Обновлено: 2026-08-27. Источник: docs/TESTING.md (регламент)</t>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Обновлено: 2026-09-06. Источник: docs/TESTING.md (регламент)</t>
         </is>
       </c>
     </row>
@@ -965,7 +1012,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>scripts/smoke.sh на обновлённой build/ib: CheckConfig + смок форм + смок печатных форм</t>
+          <t>scripts/smoke.sh на обновлённой build/ib: CheckConfig + смок форм + смок печатных форм; scripts/initial-fill-test.sh на CF, собранном из этой базы: headless-первый запуск</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -975,7 +1022,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Итог «ТЕСТЫ ПРОЙДЕНЫ» (код возврата 0). Релиз с падающими тестами не собирается</t>
+          <t>Итог «ТЕСТЫ ПРОЙДЕНЫ» и «ТЕСТ ПРОЙДЕН» (код возврата 0). Релиз с падающими тестами не собирается</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1247,11 +1294,22 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Обновлено: 2026-08-27. Данные согласованы с docs/TESTING.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Пароли начального заполнения</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Пароли headless-первого запуска (docs/DEPLOY.md) живут только в payload-файле с правами 600, который удаляется после запуска; в scripts/initial-fill.example.json — заглушки CHANGE-ME; тест генерирует пароли на лету. В result-файл, отчёт, аргументы 1cv8 и логи пароли не попадают</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1971,6 @@
         </is>
       </c>
     </row>
-    <row r="39"/>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -708,7 +708,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Проход 1: ПриСозданииНаСервере каждой формы конфигурации на новом объекте (картинки, динсписки, программное построение). Проход 2: основные формы объекта и группы, открытые с параметром Ключ по образцу из базы, — ветки, работающие только с записанным объектом. Проход 3: формирование всех печатных форм объектов из ПечатныеФормы.ОбъектыСКомандамиПечати() по образцу из базы; в тексте формы ищется номер документа-образца — если его нет, пишется ПОДОЗРЕНИЕ (пустая шапка).</t>
+          <t>Проход 1: ПриСозданииНаСервере каждой формы конфигурации на новом объекте (картинки, динсписки, программное построение). Проход 2: основные формы объекта и группы, открытые с параметром Ключ по образцу из базы, — ветки, работающие только с записанным объектом; плюс неосновные формы из явного списка ДополнительныеФормыОбъектов() (формы роли ECommerce, формы единицы и упаковки). Проход 3: формирование всех печатных форм объектов из ПечатныеФормы.ОбъектыСКомандамиПечати() по образцу из базы; в тексте формы ищется номер документа-образца — если его нет, пишется ПОДОЗРЕНИЕ (пустая шапка).</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Обработка НачальноеЗаполнение заводит организацию, пользователей, физлица и служебного администратора из JSON (docs/DEPLOY.md). Тест: пустая база из CF; первое заполнение — success, все created=true, organizations_total и users_total &gt; 0 (визард первого запуска не откроется), слова password в result нет; повтор под созданным администратором — success, всё created=false; scripts/smoke.sh на этой базе — ТЕСТЫ ПРОЙДЕНЫ.</t>
+          <t>Обработка НачальноеЗаполнение заводит организацию, пользователей, физлица и служебного администратора из JSON (docs/DEPLOY.md). Тест: пустая база из CF; первое заполнение — success, все created=true, organizations_total и users_total &gt; 0 (визард первого запуска не откроется), слова password в result нет; industry_attributes_created=4 (образец payload — отрасль «Строительство»); повтор под созданным администратором — success, всё created=false, industry_attributes_created=0; scripts/smoke.sh на этой базе — ТЕСТЫ ПРОЙДЕНЫ.</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -797,37 +797,37 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Создание / запись / проведение</t>
+          <t>ТестыДокументов: девять сценариев в транзакции с откатом</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Ключевые документы (ЗаказПокупателя, РеализацияТоваровУслуг, выпуск продукции): создание, заполнение, запись, проведение, движения по регистрам — в транзакции с откатом</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта.</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>План: серверные тесты (обработка или YAxUnit)</t>
+          <t>scripts/doctests.sh [каталог-базы] (ENTERPRISE /C "ТестыДокументов;отчёт"); интерактивно — открыть обработку ТестыДокументов</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>build/doctests-report.txt: СТАРТ;Сценариев=N; ОК;сценарий;что проверено; ОШИБКА;сценарий;описание (с сообщениями из ОбработкаПроведения); ПРОПУСК;сценарий;причина; ИТОГ;Сценариев=N;Ошибок=M;Пропущено=K. Клиентский лог build/doctests-client.log</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Машина; на живой базе — вне рабочего времени (блокировки)</t>
+          <t>Машина — на build/ib; человек — на копиях баз клиентов как приёмочный контроль (данные не меняются)</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Нет (откат транзакции)</t>
+          <t>Нет — транзакция каждого сценария откатывается</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>План: при появлении потребности</t>
+          <t>Реализован</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Обновлено: 2026-09-06. Источник: docs/TESTING.md (регламент)</t>
+          <t>Обновлено: 2026-09-08. Источник: docs/TESTING.md (регламент)</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>scripts/smoke.sh на обновлённой build/ib: CheckConfig + смок форм + смок печатных форм; scripts/initial-fill-test.sh на CF, собранном из этой базы: headless-первый запуск</t>
+          <t>scripts/smoke.sh на обновлённой build/ib: CheckConfig + смок форм + смок печатных форм; scripts/doctests.sh на ней же: жизненный цикл документов; scripts/initial-fill-test.sh на CF, собранном из этой базы: headless-первый запуск</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Итог «ТЕСТЫ ПРОЙДЕНЫ» и «ТЕСТ ПРОЙДЕН» (код возврата 0). Релиз с падающими тестами не собирается</t>
+          <t>Итоги «ТЕСТЫ ПРОЙДЕНЫ» (смок и тесты документов) и «ТЕСТ ПРОЙДЕН» (код возврата 0). Релиз с падающими тестами не собирается</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Разбор каждой строки ОШИБКА; из build/smoke-report.txt: дефект чинится, легитимный случай — в ПропускаемыеФормы() с причиной и в этот реестр</t>
+          <t>Разбор каждой строки ОШИБКА; из build/smoke-report.txt и build/doctests-report.txt: дефект чинится, легитимный случай — в ПропускаемыеФормы() с причиной и в этот реестр</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -1136,7 +1136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Новый функционал не считается законченным без расширения тестов: новые формы автоматически попадают в смок-перебор, но прогон обязателен; для нового документооборота (с появлением уровня 3) добавляется тест создание/запись/проведение; изменения состава тестов фиксируются в этом файле и в docs/TESTING.md</t>
+          <t>Новый функционал не считается законченным без расширения тестов: новые формы автоматически попадают в смок-перебор, но прогон обязателен (неосновная форма объекта — строка в ДополнительныеФормыОбъектов()); для нового документооборота добавляется сценарий в обработку ТестыДокументов (имя в ИменаСценариев, ветка в СценарийПоИмени, функция Сценарий&lt;Имя&gt;); изменения состава тестов фиксируются в этом файле и в docs/TESTING.md</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Объекты тестов — в подсистеме «Автотесты» (обработка СмокТест и общий модуль АвтотестыКлиент); подсистема не входит в командный интерфейс. Серверная логика прогона — в модуле менеджера обработки, модуль формы только запускает прогон и пишет отчёт. Скрипты — в scripts/.</t>
+          <t>Объекты тестов — в подсистеме «Автотесты» (обработки СмокТест, ТестовыеДанные, ТестыДокументов и общий модуль АвтотестыКлиент); подсистема не входит в командный интерфейс. Серверная логика прогона — в модуле менеджера обработки, модуль формы только запускает прогон и пишет отчёт. Скрипты — в scripts/.</t>
         </is>
       </c>
     </row>
@@ -1290,14 +1290,15 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Форма объекта, открытая без параметров, выполняется на новом объекте: ветки «только для записанного объекта» так не проверяются. Проход 2 смока открывает основную форму объекта и группы с параметром Ключ по образцу из базы. Неосновные формы объекта (подставляемые ОбработкойПолученияФормы) проходом не покрыты — во время выполнения форму объекта от формы списка отличить нельзя.</t>
-        </is>
-      </c>
-    </row>
+          <t>Форма объекта, открытая без параметров, выполняется на новом объекте: ветки «только для записанного объекта» так не проверяются. Проход 2 смока открывает основную форму объекта и группы с параметром Ключ по образцу из базы. Неосновные формы объекта (подставляемые ОбработкойПолученияФормы) во время выполнения от форм списка не отличить — они ведутся явным списком ДополнительныеФормыОбъектов() в модуле менеджера СмокТест; новая подстановка — строка в список.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Обновлено: 2026-08-27. Данные согласованы с docs/TESTING.md.</t>
+          <t>Обновлено: 2026-09-08. Данные согласованы с docs/TESTING.md.</t>
         </is>
       </c>
     </row>
@@ -1310,6 +1311,18 @@
       <c r="B16" t="inlineStr">
         <is>
           <t>Пароли headless-первого запуска (docs/DEPLOY.md) живут только в payload-файле с правами 600, который удаляется после запуска; в scripts/initial-fill.example.json — заглушки CHANGE-ME; тест генерирует пароли на лету. В result-файл, отчёт, аргументы 1cv8 и логи пароли не попадают</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Тесты документов не оставляют данных</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Каждый сценарий уровня 3 выполняется в транзакции, которую обработка откатывает и после успеха, и после ошибки; фиксации нет намеренно. Поэтому прогон можно запускать на копии базы клиента. Данные сценария (контрагент, склад, касса, счёт, номенклатура) заводятся заново внутри транзакции с пометкой «Тест уровня 3»; из базы берутся только организация и валюта регламентированного учёта.</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -802,7 +802,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта.</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта.</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -1114,7 +1114,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
@@ -1294,7 +1293,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
